--- a/erp-server/erp-server-scm/src/main/resources/excel/purchasePriceTemplate.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/purchasePriceTemplate.xlsx
@@ -1,15 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24225" windowHeight="12540"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="4" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -17,6 +30,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Admin</author>
+    <author>Administrator</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
@@ -79,7 +93,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="M1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+未填写则默认9999-12-31</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -96,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <r>
       <rPr>
@@ -265,20 +301,23 @@
     </r>
   </si>
   <si>
+    <t>失效时间</t>
+  </si>
+  <si>
     <t>启用状态</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="30">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -314,38 +353,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -365,6 +382,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -374,41 +430,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -459,7 +483,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -481,6 +526,12 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -491,49 +542,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -545,121 +680,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,21 +733,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -729,6 +765,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -785,152 +836,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -959,57 +1010,60 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1282,7 +1336,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="34.8571428571429" customWidth="1"/>
@@ -1290,10 +1344,11 @@
     <col min="4" max="4" width="27.2857142857143" customWidth="1"/>
     <col min="5" max="5" width="31.7142857142857" style="1" customWidth="1"/>
     <col min="6" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:14">
+    <row r="1" ht="14.25" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1330,12 +1385,15 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7"/>
+      <c r="N1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="7"/>
     </row>
-    <row r="2" ht="13.5" spans="1:14">
+    <row r="2" ht="13.5" spans="1:15">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1348,10 +1406,11 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="7"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="7"/>
     </row>
-    <row r="3" ht="13.5" spans="1:14">
+    <row r="3" ht="13.5" spans="1:15">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1364,10 +1423,11 @@
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="7"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="7"/>
     </row>
-    <row r="4" ht="13.5" spans="1:14">
+    <row r="4" ht="13.5" spans="1:15">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1380,10 +1440,11 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="7"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="7"/>
     </row>
-    <row r="5" ht="13.5" spans="2:14">
+    <row r="5" ht="13.5" spans="2:15">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -1395,10 +1456,11 @@
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="7"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="7"/>
     </row>
-    <row r="6" ht="13.5" spans="2:14">
+    <row r="6" ht="13.5" spans="2:15">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -1410,10 +1472,11 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="7"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="7"/>
     </row>
-    <row r="7" ht="13.5" spans="2:14">
+    <row r="7" ht="13.5" spans="2:15">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -1425,10 +1488,11 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="7"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="7"/>
     </row>
-    <row r="8" ht="13.5" spans="1:14">
+    <row r="8" ht="13.5" spans="1:15">
       <c r="A8" s="6"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1441,10 +1505,11 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="7"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="7"/>
     </row>
-    <row r="9" ht="13.5" spans="1:14">
+    <row r="9" ht="13.5" spans="1:15">
       <c r="A9" s="6"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1457,10 +1522,11 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="7"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="7"/>
     </row>
-    <row r="10" ht="13.5" spans="1:14">
+    <row r="10" ht="13.5" spans="1:15">
       <c r="A10" s="6"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1473,10 +1539,11 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="7"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="7"/>
     </row>
-    <row r="11" ht="13.5" spans="1:14">
+    <row r="11" ht="13.5" spans="1:15">
       <c r="A11" s="6"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1489,10 +1556,11 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="7"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="7"/>
     </row>
-    <row r="12" ht="13.5" spans="1:14">
+    <row r="12" ht="13.5" spans="1:15">
       <c r="A12" s="6"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1505,10 +1573,11 @@
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="7"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="7"/>
     </row>
-    <row r="13" ht="13.5" spans="1:14">
+    <row r="13" ht="13.5" spans="1:15">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1521,10 +1590,11 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="7"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="7"/>
     </row>
-    <row r="14" ht="13.5" spans="1:14">
+    <row r="14" ht="13.5" spans="1:15">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1537,10 +1607,11 @@
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="7"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="7"/>
     </row>
-    <row r="15" ht="13.5" spans="1:14">
+    <row r="15" ht="13.5" spans="1:15">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1553,10 +1624,11 @@
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="7"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="7"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1569,10 +1641,11 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:15">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1585,12 +1658,13 @@
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
       <formula1>"启用,停用"</formula1>
     </dataValidation>
   </dataValidations>

--- a/erp-server/erp-server-scm/src/main/resources/excel/purchasePriceTemplate.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/purchasePriceTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="4" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -45,7 +45,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -69,7 +69,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -81,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -93,7 +93,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="1">
+    <comment ref="N1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -115,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -132,25 +132,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
       <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>供应商名称</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是否含税</t>
     </r>
   </si>
   <si>
@@ -181,12 +189,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -328,6 +330,12 @@
     <font>
       <sz val="10.5"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -340,20 +348,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9.75"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -512,13 +514,13 @@
     <font>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -994,25 +996,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1336,335 +1338,357 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="34.8571428571429" customWidth="1"/>
-    <col min="2" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="27.2857142857143" customWidth="1"/>
-    <col min="5" max="5" width="31.7142857142857" style="1" customWidth="1"/>
-    <col min="6" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="27.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="31.7142857142857" style="1" customWidth="1"/>
+    <col min="7" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="20" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:15">
+    <row r="1" ht="14.25" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7"/>
+      <c r="O1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="8"/>
     </row>
-    <row r="2" ht="13.5" spans="1:15">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="5"/>
+    <row r="2" ht="13.5" spans="1:16">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
       <c r="O2" s="7"/>
+      <c r="P2" s="8"/>
     </row>
-    <row r="3" ht="13.5" spans="1:15">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="5"/>
+    <row r="3" ht="13.5" spans="1:16">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
       <c r="O3" s="7"/>
+      <c r="P3" s="8"/>
     </row>
-    <row r="4" ht="13.5" spans="1:15">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="5"/>
+    <row r="4" ht="13.5" spans="1:16">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
       <c r="O4" s="7"/>
+      <c r="P4" s="8"/>
     </row>
-    <row r="5" ht="13.5" spans="2:15">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="5"/>
+    <row r="5" ht="13.5" spans="1:16">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
       <c r="O5" s="7"/>
+      <c r="P5" s="8"/>
     </row>
-    <row r="6" ht="13.5" spans="2:15">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="5"/>
+    <row r="6" ht="13.5" spans="1:16">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
       <c r="O6" s="7"/>
+      <c r="P6" s="8"/>
     </row>
-    <row r="7" ht="13.5" spans="2:15">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="5"/>
+    <row r="7" ht="13.5" spans="1:16">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
       <c r="O7" s="7"/>
+      <c r="P7" s="8"/>
     </row>
-    <row r="8" ht="13.5" spans="1:15">
-      <c r="A8" s="6"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="5"/>
+    <row r="8" ht="13.5" spans="1:16">
+      <c r="A8" s="9"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
       <c r="O8" s="7"/>
+      <c r="P8" s="8"/>
     </row>
-    <row r="9" ht="13.5" spans="1:15">
-      <c r="A9" s="6"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="5"/>
+    <row r="9" ht="13.5" spans="1:16">
+      <c r="A9" s="9"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
       <c r="O9" s="7"/>
+      <c r="P9" s="8"/>
     </row>
-    <row r="10" ht="13.5" spans="1:15">
-      <c r="A10" s="6"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="5"/>
+    <row r="10" ht="13.5" spans="1:16">
+      <c r="A10" s="9"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
       <c r="O10" s="7"/>
+      <c r="P10" s="8"/>
     </row>
-    <row r="11" ht="13.5" spans="1:15">
-      <c r="A11" s="6"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="5"/>
+    <row r="11" ht="13.5" spans="1:16">
+      <c r="A11" s="9"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
       <c r="O11" s="7"/>
+      <c r="P11" s="8"/>
     </row>
-    <row r="12" ht="13.5" spans="1:15">
-      <c r="A12" s="6"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="5"/>
+    <row r="12" ht="13.5" spans="1:16">
+      <c r="A12" s="9"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
       <c r="O12" s="7"/>
+      <c r="P12" s="8"/>
     </row>
-    <row r="13" ht="13.5" spans="1:15">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="5"/>
+    <row r="13" ht="13.5" spans="1:16">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
       <c r="O13" s="7"/>
+      <c r="P13" s="8"/>
     </row>
-    <row r="14" ht="13.5" spans="1:15">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="5"/>
+    <row r="14" ht="13.5" spans="1:16">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
       <c r="O14" s="7"/>
+      <c r="P14" s="8"/>
     </row>
-    <row r="15" ht="13.5" spans="1:15">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="5"/>
+    <row r="15" ht="13.5" spans="1:16">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
       <c r="O15" s="7"/>
+      <c r="P15" s="8"/>
     </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+    <row r="16" spans="1:16">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
       <c r="N16" s="8"/>
-      <c r="O16" s="7"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="8"/>
     </row>
-    <row r="17" spans="1:15">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
+    <row r="17" spans="1:16">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
       <c r="N17" s="8"/>
-      <c r="O17" s="7"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="8"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
+  <dataValidations count="3">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576">
       <formula1>"启用,停用"</formula1>
     </dataValidation>
   </dataValidations>
